--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>`TWHA-SocialHistory-BetelNut` 各 `component.code` 之本地代碼。前三碼與上游 TWCR_SF `sf-BetNutChewBeh` 之 `amount`／`year`／`quit` 為 1:1 對應。（**provisional**：隨本指引之嚼檳榔建模待主管機關確認，M-5。）</t>
+    <t>【主管機關：國民健康署】`TWHA-SocialHistory-BetelNut` 各 `component.code` 之本地代碼。前三碼與上游 TWCR_SF `sf-BetNutChewBeh` 之 `amount`／`year`／`quit` 為 1:1 對應。（**provisional**：隨本指引之嚼檳榔建模待主管機關確認，M-5。）</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -153,10 +153,10 @@
     <t>duration-years</t>
   </si>
   <si>
-    <t>嚼食年數</t>
-  </si>
-  <si>
-    <t>嚼食檳榔之總年數，以 UCUM `a` 表達。對應上游 sf-BetNutChewBeh#year。</t>
+    <t>嚼食持續期間</t>
+  </si>
+  <si>
+    <t>嚼食檳榔之持續期間（嚼了多久），以 UCUM `a` 或 `mo` 表達，**以原始採集粒度為準**（不得將「嚼 2 年」逕行改寫為 24 個月）。承載主管機關最小上傳集第 11 列（醫令 30907X-3「嚼檳月數」，經主管機關答覆確認其語意為嚼食持續期間而非戒檳月數）。對應上游 sf-BetNutChewBeh#year。⚠️ 代碼 id 保留 `duration-years` 係因該碼已於 v0.4.0 發佈，改名屬破壞性變更；真實語意以本顯示名與定義為準。</t>
   </si>
   <si>
     <t>cessation-duration</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -165,7 +165,7 @@
     <t>戒除期間</t>
   </si>
   <si>
-    <t>已戒除之期間，以 UCUM `a` 或 `mo` 表達，**以原始採集粒度為準**（不得將「已戒 1 年」逕行改寫為 12 個月，見 JOB-29 §A.6）。對應上游 sf-BetNutChewBeh#quit。</t>
+    <t>已戒除之期間，以 UCUM `a` 或 `mo` 表達，**以原始採集粒度為準**（不得將「已戒 1 年」逕行改寫為 12 個月）。對應上游 sf-BetNutChewBeh#quit。</t>
   </si>
   <si>
     <t>cessation-date</t>
@@ -174,7 +174,7 @@
     <t>戒除日期</t>
   </si>
   <si>
-    <t>戒除之日期（得僅至年或年月）。**日期為原始事實，期間為導出值**——期間會隨檢查日改變，故兩者並存時以本欄為準（JOB-29 附錄 B.3）。**不得由「已戒 N 年」回推本欄**。</t>
+    <t>戒除之日期（得僅至年或年月）。**日期為原始事實，期間為導出值**——期間會隨檢查日改變，故兩者並存時以本欄為準。**不得由「已戒 N 年」回推本欄**。</t>
   </si>
   <si>
     <t>with-tobacco</t>
@@ -183,7 +183,7 @@
     <t>是否含菸草</t>
   </si>
   <si>
-    <t>所嚼食之檳榔是否含菸草。IARC 對含／不含菸草之檳榔分開評估，故流行病學分析需要此欄（JOB-29 附錄 B.1 #5）。</t>
+    <t>所嚼食之檳榔是否含菸草。IARC 對含／不含菸草之檳榔分開評估，故流行病學分析需要此欄。</t>
   </si>
   <si>
     <t>additive</t>
@@ -219,7 +219,7 @@
     <t>每日嚼食量（上游級距碼）</t>
   </si>
   <si>
-    <t>以上游 TWCR_SF 級距碼表達之每日嚼食量，供與癌症登記勾稽之用。**可選、綁定強度 extensible**——移除本 component 不影響任何核心資料（JOB-29 路徑 C-2）。</t>
+    <t>以上游 TWCR_SF 級距碼表達之每日嚼食量，供與癌症登記勾稽之用。**可選、綁定強度 extensible**——移除本 component 不影響任何核心資料。</t>
   </si>
 </sst>
 </file>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -147,7 +147,7 @@
     <t>每日嚼食量</t>
   </si>
   <si>
-    <t>每日嚼食檳榔之顆數，以 UCUM `{quid}/d` 表達。對應上游 sf-BetNutChewBeh#amount。</t>
+    <t>每日嚼食檳榔之顆數，以 UCUM 單位「{quid}/d」表達。對應上游 sf-BetNutChewBeh#amount。</t>
   </si>
   <si>
     <t>duration-years</t>
@@ -156,7 +156,7 @@
     <t>嚼食持續期間</t>
   </si>
   <si>
-    <t>嚼食檳榔之持續期間（嚼了多久），以 UCUM `a` 或 `mo` 表達，**以原始採集粒度為準**（不得將「嚼 2 年」逕行改寫為 24 個月）。承載主管機關最小上傳集第 11 列（醫令 30907X-3「嚼檳月數」，經主管機關答覆確認其語意為嚼食持續期間而非戒檳月數）。對應上游 sf-BetNutChewBeh#year。⚠️ 代碼 id 保留 `duration-years` 係因該碼已於 v0.4.0 發佈，改名屬破壞性變更；真實語意以本顯示名與定義為準。</t>
+    <t>嚼食檳榔之持續期間（嚼了多久），以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「嚼 2 年」逕行改寫為 24 個月。承載主管機關最小上傳集第 11 列（醫令 30907X-3「嚼檳月數」，經主管機關答覆確認其語意為嚼食持續期間而非戒檳月數）。對應上游 sf-BetNutChewBeh#year。⚠️ 代碼 id 保留「duration-years」係因該碼已於 v0.4.0 發佈，改名屬破壞性變更；真實語意以本顯示名與定義為準。</t>
   </si>
   <si>
     <t>cessation-duration</t>
@@ -165,7 +165,7 @@
     <t>戒除期間</t>
   </si>
   <si>
-    <t>已戒除之期間，以 UCUM `a` 或 `mo` 表達，**以原始採集粒度為準**（不得將「已戒 1 年」逕行改寫為 12 個月）。對應上游 sf-BetNutChewBeh#quit。</t>
+    <t>已戒除之期間，以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「已戒 1 年」逕行改寫為 12 個月。對應上游 sf-BetNutChewBeh#quit。</t>
   </si>
   <si>
     <t>cessation-date</t>
@@ -174,7 +174,7 @@
     <t>戒除日期</t>
   </si>
   <si>
-    <t>戒除之日期（得僅至年或年月）。**日期為原始事實，期間為導出值**——期間會隨檢查日改變，故兩者並存時以本欄為準。**不得由「已戒 N 年」回推本欄**。</t>
+    <t>戒除之日期（得僅至年或年月）。日期為原始事實，期間為導出值——期間會隨檢查日改變，故兩者並存時以本欄為準。⚠️ 不得由「已戒 N 年」回推本欄。</t>
   </si>
   <si>
     <t>with-tobacco</t>
@@ -219,7 +219,7 @@
     <t>每日嚼食量（上游級距碼）</t>
   </si>
   <si>
-    <t>以上游 TWCR_SF 級距碼表達之每日嚼食量，供與癌症登記勾稽之用。**可選、綁定強度 extensible**——移除本 component 不影響任何核心資料。</t>
+    <t>以上游 TWCR_SF 級距碼表達之每日嚼食量，供與癌症登記勾稽之用。本 component 為可選，綁定強度 extensible——移除本 component 不影響任何核心資料。</t>
   </si>
 </sst>
 </file>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -147,7 +147,7 @@
     <t>每日嚼食量</t>
   </si>
   <si>
-    <t>每日嚼食檳榔之顆數，以 UCUM 單位「{quid}/d」表達。對應上游 sf-BetNutChewBeh#amount。</t>
+    <t>每日嚼食檳榔之顆數，以 UCUM 單位「{quid}/d」表達。承載主管機關最小上傳集第 10 列（醫令 30907X-2「嚼檳量」）。⚠️ 原案該列為複合欄位，同時收「平均每日嚼幾顆」與「嚼檳年數」兩個量綱不同之值，於資料交換時難以拆解；經本案專家會議［專家會議場次與日期待補］決議，年數移列第 11 列，本欄僅承載每日顆數。單位原案記「{個}/d」，惟 UCUM 之 annotation 僅接受可列印 ASCII，「{個}」非合法 UCUM，故採「{quid}/d」——此為術語技術正確性之更正，不涉語意，數值意義完全相同。本項屬受託團隊職權範圍之技術決議，無須委託單位或主管機關另行核定。對應上游 sf-BetNutChewBeh#amount。</t>
   </si>
   <si>
     <t>duration-years</t>
@@ -156,7 +156,7 @@
     <t>嚼食持續期間</t>
   </si>
   <si>
-    <t>嚼食檳榔之持續期間（嚼了多久），以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「嚼 2 年」逕行改寫為 24 個月。承載主管機關最小上傳集第 11 列（醫令 30907X-3「嚼檳月數」，經主管機關答覆確認其語意為嚼食持續期間而非戒檳月數）。對應上游 sf-BetNutChewBeh#year。⚠️ 代碼 id 保留「duration-years」係因該碼已於 v0.4.0 發佈，改名屬破壞性變更；真實語意以本顯示名與定義為準。</t>
+    <t>嚼食檳榔之持續期間（嚼了多久），以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「嚼 2 年」逕行改寫為 24 個月。承載主管機關最小上傳集第 11 列（醫令 30907X-3，原案欄名「嚼檳月數」）。⚠️ 本欄不論受檢者現仍嚼食或已戒除，均應填列——嚼食持續期間是檳榔相關口腔癌之核心累積暴露指標，不因戒除而消失。戒除資訊另由 cessationDuration（戒除期間）與 cessationDate（戒除日期）承載，不佔上傳集之列位。原案該列之 r4 值規則寫「填寫戒檳月數」，經本案專家會議［專家會議場次與日期待補］指出係原案文字有誤並決議更正為嚼食持續期間；本項屬受託團隊職權範圍之技術決議，無須委託單位或主管機關另行核定。對應上游 sf-BetNutChewBeh#year。⚠️ 代碼 id 保留「duration-years」係因該碼已於 v0.4.0 發佈，改名屬破壞性變更；真實語意以本顯示名與定義為準。</t>
   </si>
   <si>
     <t>cessation-duration</t>
@@ -165,7 +165,7 @@
     <t>戒除期間</t>
   </si>
   <si>
-    <t>已戒除之期間，以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「已戒 1 年」逕行改寫為 12 個月。對應上游 sf-BetNutChewBeh#quit。</t>
+    <t>已戒除之期間，以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「已戒 1 年」逕行改寫為 12 個月。⚠️ 本欄與 cessationDate 共同承接主管機關原案第 11 列 r4 所指之「戒檳月數」：該列語意經本案專家會議決議更正為嚼食持續期間後，戒除資訊改由本欄承載，不佔上傳集之列位。故本次語意更正並不造成任何資訊遺失。對應上游 sf-BetNutChewBeh#quit。</t>
   </si>
   <si>
     <t>cessation-date</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -147,7 +147,7 @@
     <t>每日嚼食量</t>
   </si>
   <si>
-    <t>每日嚼食檳榔之顆數，以 UCUM 單位「{quid}/d」表達。承載主管機關最小上傳集第 10 列（醫令 30907X-2「嚼檳量」）。⚠️ 原案該列為複合欄位，同時收「平均每日嚼幾顆」與「嚼檳年數」兩個量綱不同之值，於資料交換時難以拆解；經本案專家會議［專家會議場次與日期待補］決議，年數移列第 11 列，本欄僅承載每日顆數。單位原案記「{個}/d」，惟 UCUM 之 annotation 僅接受可列印 ASCII，「{個}」非合法 UCUM，故採「{quid}/d」——此為術語技術正確性之更正，不涉語意，數值意義完全相同。本項屬受託團隊職權範圍之技術決議，無須委託單位或主管機關另行核定。對應上游 sf-BetNutChewBeh#amount。</t>
+    <t>每日嚼食檳榔之顆數，以 UCUM 單位「{quid}/d」表達。承載主管機關最小上傳集第 10 列（醫令 30907X-2「嚼檳量」）。⚠️ 原案該列為複合欄位，同時收「平均每日嚼幾顆」與「嚼檳年數」兩個量綱不同之值，於資料交換時難以拆解；本欄僅承載每日顆數，年數移列第 11 列——第 11 列之語意經本案專家共識會議（2026-07-17）七、臨時動議決議更正為嚼食持續期間，年數乃隨之移列。單位原案記「{個}/d」，惟 UCUM 之 annotation 僅接受可列印 ASCII，「{個}」非合法 UCUM，故採「{quid}/d」——此為術語技術正確性之更正，不涉語意，數值意義完全相同。本項屬受託團隊職權範圍之技術決議，無須委託單位或主管機關另行核定。對應上游 sf-BetNutChewBeh#amount。</t>
   </si>
   <si>
     <t>duration-years</t>
@@ -156,7 +156,7 @@
     <t>嚼食持續期間</t>
   </si>
   <si>
-    <t>嚼食檳榔之持續期間（嚼了多久），以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「嚼 2 年」逕行改寫為 24 個月。承載主管機關最小上傳集第 11 列（醫令 30907X-3，原案欄名「嚼檳月數」）。⚠️ 本欄不論受檢者現仍嚼食或已戒除，均應填列——嚼食持續期間是檳榔相關口腔癌之核心累積暴露指標，不因戒除而消失。戒除資訊另由 cessationDuration（戒除期間）與 cessationDate（戒除日期）承載，不佔上傳集之列位。原案該列之 r4 值規則寫「填寫戒檳月數」，經本案專家會議［專家會議場次與日期待補］指出係原案文字有誤並決議更正為嚼食持續期間；本項屬受託團隊職權範圍之技術決議，無須委託單位或主管機關另行核定。對應上游 sf-BetNutChewBeh#year。⚠️ 代碼 id 保留「duration-years」係因該碼已於 v0.4.0 發佈，改名屬破壞性變更；真實語意以本顯示名與定義為準。</t>
+    <t>嚼食檳榔之持續期間（嚼了多久），以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「嚼 2 年」逕行改寫為 24 個月。承載主管機關最小上傳集第 11 列（醫令 30907X-3，原案欄名「嚼檳月數」）。⚠️ 本欄不論受檢者現仍嚼食或已戒除，均應填列——嚼食持續期間是檳榔相關口腔癌之核心累積暴露指標，不因戒除而消失。戒除資訊另由 cessationDuration（戒除期間）與 cessationDate（戒除日期）承載，不佔上傳集之列位。原案該列之 r4 值規則寫「填寫戒檳月數」，經本案專家共識會議（臺灣勞工健康檢查核心資料集與 FHIR IG 專家共識討論會，2026-07-17）七、臨時動議認定係原案文字有誤，決議更正為嚼食持續期間，且不論現嚼或已戒均應填列；共同主持人曹又中主任（職業醫學科）另於 2026-07-31 回信補充說明；本項屬受託團隊職權範圍之技術決議，無須委託單位或主管機關另行核定。對應上游 sf-BetNutChewBeh#year。⚠️ 代碼 id 保留「duration-years」係因該碼已於 v0.4.0 發佈，改名屬破壞性變更；真實語意以本顯示名與定義為準。</t>
   </si>
   <si>
     <t>cessation-duration</t>
@@ -165,7 +165,7 @@
     <t>戒除期間</t>
   </si>
   <si>
-    <t>已戒除之期間，以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「已戒 1 年」逕行改寫為 12 個月。⚠️ 本欄與 cessationDate 共同承接主管機關原案第 11 列 r4 所指之「戒檳月數」：該列語意經本案專家會議決議更正為嚼食持續期間後，戒除資訊改由本欄承載，不佔上傳集之列位。故本次語意更正並不造成任何資訊遺失。對應上游 sf-BetNutChewBeh#quit。</t>
+    <t>已戒除之期間，以 UCUM 單位「a」或「mo」表達，並以原始採集粒度為準——不得將「已戒 1 年」逕行改寫為 12 個月。⚠️ 本欄與 cessationDate 共同承接主管機關原案第 11 列 r4 所指之「戒檳月數」：該列語意經本案專家共識會議（2026-07-17）決議更正為嚼食持續期間後，戒除資訊改由本欄承載，不佔上傳集之列位。故本次語意更正並不造成任何資訊遺失。對應上游 sf-BetNutChewBeh#quit。</t>
   </si>
   <si>
     <t>cessation-date</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-CS-BetelNutComponent.xlsx
+++ b/CodeSystem-CS-BetelNutComponent.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
